--- a/data/raw/inventory/Week 35/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -969,7 +969,7 @@
         <v>495</v>
       </c>
       <c r="F9" t="n">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -981,7 +981,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K9" t="n">
         <v>497</v>
@@ -1028,7 +1028,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="F10" t="n">
         <v>429</v>
@@ -1043,10 +1043,10 @@
         <v>6</v>
       </c>
       <c r="J10" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="L10" t="n">
         <v>8</v>
@@ -1400,10 +1400,10 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F16" t="n">
-        <v>338</v>
+        <v>351</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1415,10 +1415,10 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="K16" t="n">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="L16" t="n">
         <v>1</v>
@@ -1589,7 +1589,7 @@
         <v>59</v>
       </c>
       <c r="F19" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -1601,7 +1601,7 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
         <v>59</v>
@@ -1651,7 +1651,7 @@
         <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -1663,7 +1663,7 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K20" t="n">
         <v>61</v>
@@ -2454,7 +2454,7 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F33" t="n">
         <v>20</v>
@@ -2469,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="J33" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K33" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2519,7 +2519,7 @@
         <v>33</v>
       </c>
       <c r="F34" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -2531,7 +2531,7 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K34" t="n">
         <v>33</v>
@@ -2705,7 +2705,7 @@
         <v>234</v>
       </c>
       <c r="F37" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -2717,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
         <v>235</v>
@@ -3074,10 +3074,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F43" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3089,10 +3089,10 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="K43" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="L43" t="n">
         <v>8</v>
@@ -3201,7 +3201,7 @@
         <v>32</v>
       </c>
       <c r="F45" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -3213,7 +3213,7 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>34</v>
@@ -4314,10 +4314,10 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="F63" t="n">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4329,10 +4329,10 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="K63" t="n">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="L63" t="n">
         <v>3</v>
@@ -4503,7 +4503,7 @@
         <v>907</v>
       </c>
       <c r="F66" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -4515,7 +4515,7 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K66" t="n">
         <v>929</v>
@@ -5058,10 +5058,10 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>832</v>
+        <v>954</v>
       </c>
       <c r="F75" t="n">
-        <v>211</v>
+        <v>333</v>
       </c>
       <c r="G75" t="n">
         <v>600</v>
@@ -5076,10 +5076,10 @@
         <v>18</v>
       </c>
       <c r="K75" t="n">
-        <v>847</v>
+        <v>970</v>
       </c>
       <c r="L75" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M75" t="n">
         <v>0</v>
@@ -5185,7 +5185,7 @@
         <v>63</v>
       </c>
       <c r="F77" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G77" t="n">
         <v>50</v>
@@ -5197,7 +5197,7 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
         <v>63</v>
@@ -6115,7 +6115,7 @@
         <v>67</v>
       </c>
       <c r="F92" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K92" t="n">
         <v>67</v>
@@ -6797,7 +6797,7 @@
         <v>351</v>
       </c>
       <c r="F103" t="n">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -6809,7 +6809,7 @@
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K103" t="n">
         <v>352</v>
@@ -7414,7 +7414,7 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="F113" t="n">
         <v>1</v>
@@ -7429,10 +7429,10 @@
         <v>0</v>
       </c>
       <c r="J113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K113" t="n">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="L113" t="n">
         <v>3</v>
@@ -7479,7 +7479,7 @@
         <v>80</v>
       </c>
       <c r="F114" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K114" t="n">
         <v>80</v>
@@ -7789,7 +7789,7 @@
         <v>43</v>
       </c>
       <c r="F119" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -7801,7 +7801,7 @@
         <v>0</v>
       </c>
       <c r="J119" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K119" t="n">
         <v>45</v>
@@ -8344,7 +8344,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F128" t="n">
         <v>74</v>
@@ -8359,10 +8359,10 @@
         <v>0</v>
       </c>
       <c r="J128" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L128" t="n">
         <v>2</v>
@@ -9649,7 +9649,7 @@
         <v>125</v>
       </c>
       <c r="F149" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -9661,7 +9661,7 @@
         <v>0</v>
       </c>
       <c r="J149" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K149" t="n">
         <v>125</v>
@@ -10204,7 +10204,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F158" t="n">
         <v>148</v>
@@ -10219,10 +10219,10 @@
         <v>5</v>
       </c>
       <c r="J158" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K158" t="n">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="L158" t="n">
         <v>2</v>
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="F161" t="n">
         <v>45</v>
@@ -10405,10 +10405,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L161" t="n">
         <v>1</v>
@@ -10638,10 +10638,10 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="F165" t="n">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="G165" t="n">
         <v>240</v>
@@ -10653,10 +10653,10 @@
         <v>0</v>
       </c>
       <c r="J165" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K165" t="n">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="L165" t="n">
         <v>3</v>

--- a/data/raw/inventory/Week 35/Nexlev/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 35/Nexlev/Seller FBA Inventory (SP-API).xlsx
@@ -1028,16 +1028,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1253</v>
+        <v>1252</v>
       </c>
       <c r="F10" t="n">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="G10" t="n">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>61</v>
+        <v>781</v>
       </c>
       <c r="I10" t="n">
         <v>6</v>
@@ -1046,10 +1046,10 @@
         <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M10" t="n">
         <v>4</v>
@@ -1403,7 +1403,7 @@
         <v>526</v>
       </c>
       <c r="F16" t="n">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -1415,7 +1415,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
         <v>527</v>
@@ -1834,7 +1834,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F23" t="n">
         <v>151</v>
@@ -1849,10 +1849,10 @@
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K23" t="n">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F34" t="n">
         <v>30</v>
@@ -2531,10 +2531,10 @@
         <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K34" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F37" t="n">
         <v>72</v>
@@ -2717,10 +2717,10 @@
         <v>0</v>
       </c>
       <c r="J37" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K37" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L37" t="n">
         <v>1</v>
@@ -3077,7 +3077,7 @@
         <v>398</v>
       </c>
       <c r="F43" t="n">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -3089,13 +3089,13 @@
         <v>0</v>
       </c>
       <c r="J43" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="L43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M43" t="n">
         <v>0</v>
@@ -4317,7 +4317,7 @@
         <v>926</v>
       </c>
       <c r="F63" t="n">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -4329,7 +4329,7 @@
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K63" t="n">
         <v>929</v>
@@ -4518,10 +4518,10 @@
         <v>7</v>
       </c>
       <c r="K66" t="n">
-        <v>929</v>
+        <v>927</v>
       </c>
       <c r="L66" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="M66" t="n">
         <v>3</v>
@@ -5058,25 +5058,25 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>954</v>
+        <v>959</v>
       </c>
       <c r="F75" t="n">
-        <v>333</v>
+        <v>340</v>
       </c>
       <c r="G75" t="n">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>603</v>
       </c>
       <c r="I75" t="n">
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K75" t="n">
-        <v>970</v>
+        <v>975</v>
       </c>
       <c r="L75" t="n">
         <v>16</v>
@@ -6735,7 +6735,7 @@
         <v>126</v>
       </c>
       <c r="F102" t="n">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -6747,7 +6747,7 @@
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K102" t="n">
         <v>126</v>
@@ -7228,7 +7228,7 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F110" t="n">
         <v>171</v>
@@ -7243,10 +7243,10 @@
         <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K110" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L110" t="n">
         <v>0</v>
@@ -7293,7 +7293,7 @@
         <v>95</v>
       </c>
       <c r="F111" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K111" t="n">
         <v>95</v>
@@ -8412,10 +8412,10 @@
         <v>169</v>
       </c>
       <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
         <v>240</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
       </c>
       <c r="I129" t="n">
         <v>0</v>
@@ -10207,7 +10207,7 @@
         <v>244</v>
       </c>
       <c r="F158" t="n">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G158" t="n">
         <v>90</v>
@@ -10219,7 +10219,7 @@
         <v>5</v>
       </c>
       <c r="J158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K158" t="n">
         <v>246</v>
@@ -10393,7 +10393,7 @@
         <v>263</v>
       </c>
       <c r="F161" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G161" t="n">
         <v>12</v>
@@ -10405,7 +10405,7 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K161" t="n">
         <v>264</v>
@@ -10644,10 +10644,10 @@
         <v>98</v>
       </c>
       <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
         <v>240</v>
-      </c>
-      <c r="H165" t="n">
-        <v>0</v>
       </c>
       <c r="I165" t="n">
         <v>0</v>
